--- a/Experiments/7194/files/SyrsWorks/secstubs.xlsx
+++ b/Experiments/7194/files/SyrsWorks/secstubs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593A434B-D6A2-4C46-A242-50569C262371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="760" windowWidth="33580" windowHeight="21580" xr2:uid="{AB3695C3-3BD0-BD42-8977-4EE2808F5EEB}"/>
+    <workbookView xWindow="980" yWindow="760" windowWidth="33580" windowHeight="21580" activeTab="1" xr2:uid="{AB3695C3-3BD0-BD42-8977-4EE2808F5EEB}"/>
   </bookViews>
   <sheets>
     <sheet name="AI Prompt" sheetId="5" r:id="rId1"/>
